--- a/Department_BillableData_Development.xlsx
+++ b/Department_BillableData_Development.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Billable Type</t>
   </si>
@@ -30,9 +30,6 @@
   </si>
   <si>
     <t>InternalRNDProducts</t>
-  </si>
-  <si>
-    <t>Shadow</t>
   </si>
   <si>
     <t>TNM</t>
@@ -120,11 +117,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="20.1875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.74609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.0859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -145,7 +142,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>35.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="4">
@@ -153,7 +150,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="5">
@@ -161,7 +158,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>2.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="6">
@@ -169,15 +166,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="n">
-        <v>50.0</v>
+        <v>26.0</v>
       </c>
     </row>
   </sheetData>

--- a/Department_BillableData_Development.xlsx
+++ b/Department_BillableData_Development.xlsx
@@ -142,7 +142,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="4">
@@ -150,7 +150,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="5">
@@ -158,7 +158,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>23.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="6">
@@ -166,7 +166,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
   </sheetData>
